--- a/media/templates/药业车间分解编排计划模板.xlsx
+++ b/media/templates/药业车间分解编排计划模板.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\药业代码\片剂药物智能排程系统算法\药业\输入\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\片剂药物智能排程系统\交互说明及模板文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="30">
   <si>
     <t>部门</t>
   </si>
@@ -58,7 +58,7 @@
     <t>210车间</t>
   </si>
   <si>
-    <t>阿司匹林肠溶片(过评)</t>
+    <t>阿司匹林肠溶片（过评）</t>
   </si>
   <si>
     <t>100mg×9片×3板×400盒</t>
@@ -70,9 +70,6 @@
     <t>100mg×10片×4板×400盒</t>
   </si>
   <si>
-    <t>阿司匹林肠溶片（过评）</t>
-  </si>
-  <si>
     <t>100mg×8片×4板×400盒</t>
   </si>
   <si>
@@ -88,25 +85,6 @@
     <t>100mg×11片×4板×400盒</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>阿司匹林肠溶片</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（过评）</t>
-    </r>
-  </si>
-  <si>
     <t>100mg×12片×2板×400盒</t>
   </si>
   <si>
@@ -125,10 +103,10 @@
     <t>100mg×13片×5板×200盒</t>
   </si>
   <si>
-    <t>100mg*14片/板*2板/盒*400盒</t>
-  </si>
-  <si>
-    <t>100mg*14片/板*4板/盒*400盒</t>
+    <t>100mg×14片/板×2板/盒×400盒</t>
+  </si>
+  <si>
+    <t>100mg×14片/板×4板/盒×400盒</t>
   </si>
   <si>
     <t>100mg×15片×2板×400盒</t>
@@ -143,16 +121,7 @@
     <t>100mg×15片×6板×400盒</t>
   </si>
   <si>
-    <t>阿司匹林肠溶片(片剂)</t>
-  </si>
-  <si>
-    <t>100mg*14片/板*5板/盒*400盒</t>
-  </si>
-  <si>
-    <t>注</t>
-  </si>
-  <si>
-    <t>当前展示的是示例数据，可删除后上传您的数据。</t>
+    <t>注：当前展示的是示例数据，可删除后上传您的数据，上传时请删除该行信息，避免影响您的使用。</t>
   </si>
 </sst>
 </file>
@@ -213,6 +182,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -355,12 +330,6 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -683,137 +652,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -859,23 +828,14 @@
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1403,19 +1363,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G24"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="15" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="8.725" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="8.72727272727273" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14.8181818181818" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8.725" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14.8166666666667" style="1" customWidth="1"/>
     <col min="3" max="3" width="23" style="2" customWidth="1"/>
-    <col min="4" max="4" width="22.4545454545455" style="3" customWidth="1"/>
-    <col min="5" max="5" width="11.5454545454545" style="4" customWidth="1"/>
-    <col min="6" max="6" width="17.6363636363636" style="5" customWidth="1"/>
-    <col min="7" max="7" width="11.3636363636364" style="6" customWidth="1"/>
-    <col min="8" max="16384" width="8.72727272727273" style="7"/>
+    <col min="4" max="4" width="22.4583333333333" style="3" customWidth="1"/>
+    <col min="5" max="5" width="11.5416666666667" style="4" customWidth="1"/>
+    <col min="6" max="6" width="17.6333333333333" style="5" customWidth="1"/>
+    <col min="7" max="7" width="11.3666666666667" style="6" customWidth="1"/>
+    <col min="8" max="16384" width="8.725" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14" spans="1:7">
+    <row r="1" ht="13.5" spans="1:7">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1438,7 +1398,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" ht="13.5" spans="1:7">
       <c r="A2" s="10" t="s">
         <v>7</v>
       </c>
@@ -1457,7 +1417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" ht="13.5" spans="1:7">
       <c r="A3" s="10" t="s">
         <v>7</v>
       </c>
@@ -1476,7 +1436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" ht="13.5" spans="1:7">
       <c r="A4" s="10" t="s">
         <v>7</v>
       </c>
@@ -1495,28 +1455,28 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="15">
+    <row r="5" ht="13.5" spans="1:7">
+      <c r="A5" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="10">
         <v>2007004220</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="17"/>
+      <c r="E5" s="12"/>
       <c r="F5" s="13">
         <v>120000</v>
       </c>
-      <c r="G5" s="18">
+      <c r="G5" s="14">
         <v>120000</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" ht="13.5" spans="1:7">
       <c r="A6" s="10" t="s">
         <v>7</v>
       </c>
@@ -1524,10 +1484,10 @@
         <v>2007004218</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E6" s="12"/>
       <c r="F6" s="13"/>
@@ -1535,7 +1495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" ht="13.5" spans="1:7">
       <c r="A7" s="10" t="s">
         <v>7</v>
       </c>
@@ -1543,10 +1503,10 @@
         <v>2007004227</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E7" s="12"/>
       <c r="F7" s="13"/>
@@ -1554,7 +1514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" ht="13.5" spans="1:7">
       <c r="A8" s="10" t="s">
         <v>7</v>
       </c>
@@ -1562,10 +1522,10 @@
         <v>2007004228</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E8" s="12"/>
       <c r="F8" s="13"/>
@@ -1573,7 +1533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" ht="13.5" spans="1:7">
       <c r="A9" s="10" t="s">
         <v>7</v>
       </c>
@@ -1581,10 +1541,10 @@
         <v>2007004229</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E9" s="12"/>
       <c r="F9" s="13"/>
@@ -1592,7 +1552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" ht="13.5" spans="1:7">
       <c r="A10" s="10" t="s">
         <v>7</v>
       </c>
@@ -1600,10 +1560,10 @@
         <v>2007004211</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E10" s="12"/>
       <c r="F10" s="13"/>
@@ -1611,7 +1571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" ht="13.5" spans="1:7">
       <c r="A11" s="10" t="s">
         <v>7</v>
       </c>
@@ -1619,10 +1579,10 @@
         <v>2007004212</v>
       </c>
       <c r="C11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="11" t="s">
         <v>18</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>20</v>
       </c>
       <c r="E11" s="12">
         <v>162800</v>
@@ -1632,7 +1592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" ht="13.5" spans="1:7">
       <c r="A12" s="10" t="s">
         <v>7</v>
       </c>
@@ -1640,10 +1600,10 @@
         <v>2007004213</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E12" s="12"/>
       <c r="F12" s="13"/>
@@ -1651,7 +1611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" ht="13.5" spans="1:7">
       <c r="A13" s="10" t="s">
         <v>7</v>
       </c>
@@ -1659,10 +1619,10 @@
         <v>2007004221</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E13" s="12"/>
       <c r="F13" s="13"/>
@@ -1670,7 +1630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" ht="13.5" spans="1:7">
       <c r="A14" s="10" t="s">
         <v>7</v>
       </c>
@@ -1678,10 +1638,10 @@
         <v>2007004230</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E14" s="12"/>
       <c r="F14" s="13"/>
@@ -1689,7 +1649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" ht="13.5" spans="1:7">
       <c r="A15" s="10" t="s">
         <v>7</v>
       </c>
@@ -1697,10 +1657,10 @@
         <v>2007004222</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E15" s="12"/>
       <c r="F15" s="13"/>
@@ -1708,7 +1668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" ht="13.5" spans="1:7">
       <c r="A16" s="10" t="s">
         <v>7</v>
       </c>
@@ -1716,10 +1676,10 @@
         <v>2007004223</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E16" s="12"/>
       <c r="F16" s="13"/>
@@ -1727,7 +1687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" ht="13.5" spans="1:7">
       <c r="A17" s="10" t="s">
         <v>7</v>
       </c>
@@ -1735,10 +1695,10 @@
         <v>2007004219</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E17" s="12"/>
       <c r="F17" s="13"/>
@@ -1746,7 +1706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" ht="13.5" spans="1:7">
       <c r="A18" s="10" t="s">
         <v>7</v>
       </c>
@@ -1754,10 +1714,10 @@
         <v>2007004214</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E18" s="12">
         <v>75200</v>
@@ -1769,7 +1729,7 @@
         <v>76666.6666666667</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" ht="13.5" spans="1:7">
       <c r="A19" s="10" t="s">
         <v>7</v>
       </c>
@@ -1777,10 +1737,10 @@
         <v>2007004216</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E19" s="12"/>
       <c r="F19" s="13"/>
@@ -1788,18 +1748,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" ht="13.5" spans="1:7">
       <c r="A20" s="10" t="s">
         <v>7</v>
       </c>
       <c r="B20" s="10">
         <v>2007004215</v>
       </c>
-      <c r="C20" s="16" t="s">
-        <v>18</v>
+      <c r="C20" s="11" t="s">
+        <v>8</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E20" s="12">
         <v>2050405</v>
@@ -1811,7 +1771,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" ht="13.5" spans="1:7">
       <c r="A21" s="10" t="s">
         <v>7</v>
       </c>
@@ -1819,41 +1779,31 @@
         <v>2007000332</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E21" s="12"/>
       <c r="F21" s="13"/>
       <c r="G21" s="14"/>
     </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" s="10">
-        <v>2007004232</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>32</v>
-      </c>
+    <row r="22" ht="13.5" spans="1:7">
+      <c r="A22" s="10"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
       <c r="E22" s="12"/>
       <c r="F22" s="13"/>
-      <c r="G22" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="B24" s="20" t="s">
-        <v>34</v>
-      </c>
+      <c r="G22" s="14"/>
+    </row>
+    <row r="24" ht="18.75" spans="1:7">
+      <c r="A24" s="15"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
